--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -95,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -111,6 +112,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I330"/>
+  <dimension ref="A1:I335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15722,7 +15724,6 @@
           <t>SiFi Networks</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>SmartOptics transceivers (primary), DWDM backbone (secondary)</t>
@@ -15834,6 +15835,231 @@
       <c r="I330" t="inlineStr">
         <is>
           <t>Dir Engineering, Verizon transmission background. Hunter just closed Oak Hill Capital deal for Oregon expansion. Optics lead. Day 1 2026-05-07. Person 6 at Hunter (+10 biz day cooling gap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Paul Merritt</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Fatbeam</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pamerritt/</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Exec supply chain / DWDM / TPM</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 216986522272</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H331" s="9" t="n">
+        <v>46133</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>CEO, 2nd degree. Hook: 1mo-old post about Western WA Enterprise team hiring during Basalt buildout. Exec angle, not sample opener.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Gavin Budd</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>VP of Network Operations and Engineering</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Fatbeam</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gavin-budd-99a7253/</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>DWDM / Optics (SFP sample wedge) / TPM</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 538744</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H332" s="9" t="n">
+        <v>46133</v>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>VP Network Ops, 2nd degree, restricted profile. Existing HubSpot contact (last touch Aug 2020). Lead SFP sample then DWDM vs Ciena/Nokia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Danny Pate</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Fatbeam</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dannypate/</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>TPM / DWDM / Pre-owned networking (COO exec angle)</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 216990632756</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H333" s="9" t="n">
+        <v>46133</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>COO, 3rd degree, active on LinkedIn. Lead TPM / OEM cost conversation. Fatbeam PE-backed expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Adam Hill</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>NOC Manager</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Fatbeam</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adam-hill-b31136229/</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>SFP break-glass / TPM / Pre-owned networking</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 216990215766</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H334" s="9" t="n">
+        <v>46133</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>NOC Manager, 3rd degree. Lead SFP break-glass for 2am failures then TPM on aging gear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Jordan Diaz</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>OSP Engineering Manager (ZI: Manager Network Operations)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Fatbeam</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jordan-diaz-095b73184/</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>DWDM / Optics / 400G ZR</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 216979127691</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H335" s="9" t="n">
+        <v>46133</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>OSP Eng Mgr / dual Network Ops Mgr per ZoomInfo. 3rd degree. Lead SFP sample then DWDM for transport buildout.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +16075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -17298,6 +17524,36 @@
       <c r="F50" t="inlineStr">
         <is>
           <t>18 emails queued to email-queue.json. LINKED_IN_CONNECT tasks 107848632473 (David), 107882380691 (Ed), 107849563414 (Joseph) marked COMPLETED. New Day-1 LinkedIn tasks created: 108266943518 (David, due 2026-04-21), 108276392767 (Ed, due 2026-04-21), 108275895457 (Joseph, due 2026-05-07). Weekend scheduled batch 27 of 38. Strategy notes already in place from 2026-04-11 qualification run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Fatbeam</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>19 qualified shortlist reviewed, 5 sequenced</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>5 sequences (Paul Merritt CEO, Gavin Budd VP Net Ops, Danny Pate COO, Adam Hill NOC Mgr, Jordan Diaz OSP/Net Ops)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Basalt Infrastructure acquiring from SDC Capital closing Q2 2026. Fatbeam owned by Andy, last contacted Aug 2020. Cold reengagement. Approved-vendor status: No. Also flagged: Gregory Green (HubSpot 355102) is former CEO, no longer at Fatbeam; contact record needs update. Katherine Stephens, Jeffrey Bulger disqualified on profile read (BI/GIS and Open To Work respectively). 6 other individual contributor engineers/NOC not sequenced (too junior for full 6-email).</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -17568,7 +17568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17659,6 +17659,39 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gary Duttenhefer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Consolidated Telcom</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hard bounce -- bad email address</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>garyduttenhefer@consolidatednd.com bounced 4/22 after email 2/6. HubSpot also shows garyduttenhefer48645152@gmail.com on record. HubSpot note added.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16060,6 +16060,141 @@
       <c r="I335" t="inlineStr">
         <is>
           <t>OSP Eng Mgr / dual Network Ops Mgr per ZoomInfo. 3rd degree. Lead SFP sample then DWDM for transport buildout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Jesse Tucker</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Network Engineer IV (DOCSIS)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Midcontinent Communications, Inc.</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jesse-tucker6128/</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Sample SFPs (Network) -&gt; DWDM (cable transport) -&gt; Cisco TPM -&gt; DIMMs</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 217781724059</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H336" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Network Eng IV DOCSIS at Midco. Wireshark Cert Analyst 1mo, DOCSIS Eng Pro, Cisco CCNP-Enterprise. SCI Broadband acquisition adding plant. Day 1 = 2026-05-28 (5th Midco person, +10 bd cooling gap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Tony Fisher</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Midcontinent Communications, Inc.</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tony-fisher-a270506/</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>DIMMs (Server) -&gt; Sample SFPs -&gt; Cisco TPM -&gt; DWDM</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 564828</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H337" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>System Engineer at Midco, 30-39 yrs exp, IT Infrastructure. HubSpot updated: jobtitle stale, phone/mobile re-keyed off switchboard. Day 1 = 2026-06-03 (6th Midco, +4 bd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Brad Janzen</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Transport Engineering Supervisor</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Midcontinent Communications, Inc.</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brad-janzen-3302917/</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>DWDM (pain-led) -&gt; Sample SFPs -&gt; Cisco TPM -&gt; DIMMs</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 217780773512</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H338" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Transport Engineering Supervisor at Midco, 30+ yrs, Manager. Direct DWDM buyer. SCI Broadband hook. Day 1 = 2026-06-09 (7th Midco, +4 bd).</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I338"/>
+  <dimension ref="A1:I347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16195,6 +16195,417 @@
       <c r="I338" t="inlineStr">
         <is>
           <t>Transport Engineering Supervisor at Midco, 30+ yrs, Manager. Direct DWDM buyer. SCI Broadband hook. Day 1 = 2026-06-09 (7th Midco, +4 bd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>John Lachance</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Lingo Communications</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jlachance/</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Sample SFPs (Network) -&gt; Cisco/Juniper TPM -&gt; DWDM (Smartoptics) -&gt; DIMMs</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 217783919683</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H339" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Sr Solutions Engineer at Lingo (3rd-degree). ZoomInfo FULL_MATCH 98%: jlachance@impacttelecom.com (legacy Lingo brand domain) + mobile (512) 635-1720. Network sample-offer w/ TPM/DWDM/DIMMs follow-on. Day 1 = 2026-04-27 (1st Lingo, person_count=0 -&gt; next bd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Colin Vesper</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Lead Network Engineer</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Visionary Broadband</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/colinvesper/</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Sample SFPs (Network) -&gt; DWDM (Smartoptics) -&gt; Cisco/Juniper TPM -&gt; DIMMs</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 217774992137</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H340" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Lead Network Engineer at Visionary Broadband (3rd-degree, Gillette WY). ZoomInfo 93%: cvesper@office.vcn.com + (307) 685-5523 direct + (307) 680-7624 mobile. Visionary is existing OSI customer at company level. Day 1 = 2026-04-27 (1st Visionary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Preston Schilling</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>COO</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Visionary Broadband</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/preston-schilling-48921626/</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>DWDM (pain-led, exec) -&gt; TPM -&gt; DIMMs -&gt; Pre owned + new networking</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 217794530995</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H341" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>COO at Visionary Broadband (1st-degree, Gillette WY). ZoomInfo 98%: pschilling@office.vcn.com + (307) 685-5545 direct + (307) 689-3416 mobile. Already 1st-degree, LINKED_IN_CONNECT skipped. Pain-led DWDM exec opener. Day 1 = 2026-05-01 (2nd Visionary, +4 bd from Colin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Sarah Frisbie</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Director, Network Engineering</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>altafiber (Cincinnati Bell)</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarahfrisbie1/</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Network sample SFPs -&gt; DWDM/transport (2027 fiber push) -&gt; TPM -&gt; DIMMs</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 46214249386 (existing, last contact 2024-08)</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live</t>
+        </is>
+      </c>
+      <c r="H342" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Director Network Engineering at altafiber. 1st-degree, 2 mutual. ZoomInfo 99 percent: sarah.frisbie@altafiber.com + (513) 565-0650 mobile. Existing HubSpot mobile (513) 314-6657. Day 1 = 2026-05-11 (Cincinnati Bell run-stagger person_count=1). Hook: altafiber publicly committed to 90 percent fiber availability by 2027. 5 other altafiber sequences in flight from Andy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Scott Pennington</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Network Engineer III / Principal Platform Engineer</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>altafiber (Cincinnati Bell)</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scott-pennington-3b0670b/</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Network sample SFPs -&gt; DWDM/transport (2027 fiber) -&gt; TPM -&gt; DIMMs</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 138771300470 (existing, last contact 2025-10-10)</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live (re-engagement)</t>
+        </is>
+      </c>
+      <c r="H343" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Senior IC at altafiber. LinkedIn says Network Engineer III, HubSpot+ZoomInfo say Principal Platform Engineer (more recent). 1st-degree (3 mutuals). ZoomInfo 91 percent: scott.pennington@altafiber.com. Day 1 = 2026-05-15. Sister sequence to Sarah Frisbie (Director, 5/11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Ron Beerman</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Chief Network Officer</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>altafiber (Cincinnati Bell)</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ron-beerman-a4407a2/</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>DWDM/transport pain-led exec -&gt; TPM -&gt; DIMMs -&gt; Pre owned + new Nokia</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Andy -- HubSpot ID 3732051 (existing since 2024-02, long re-engagement)</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Pursue -- sequence live (exec, pain-led)</t>
+        </is>
+      </c>
+      <c r="H344" s="8" t="n">
+        <v>46137</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>CNO at altafiber. 1st-degree, 1 mutual (Todd). ZoomInfo 99 percent: ron.beerman@altafiber.com + mobile (513) 608-7400. Hook: Lahaina restoration talk at FiberConnect 2025 + altafiber 90 percent fiber by 2027 commitment. Pain-led exec opener (SmartOptics DCP DWDM vs Ciena/Nokia, 30-50 percent below). Day 1 = 2026-05-21. Sister sequences: Frisbie (5/11), Pennington (5/15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Stephen Linde</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Director, Procurement</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>altafiber</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/steve-linde-20403140/</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Pain-led DWDM/transport intro to Procurement Director, expand to TPM + DIMMs + pre-owned across the sequence</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>1st degree, LINKED_IN_CONNECT skipped. Day 1 2026-05-28. Cincinnati Bell stagger person 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Justin Pastore</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Senior Network and Security Engineer</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Armstrong Group of Companies</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/justin-pastore-39b79880/</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP), pivot to DWDM, TPM, DIMMs, and pre-owned gear</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Existing HubSpot 539547. Day 1 2026-04-27 (Mon). 3rd-degree LinkedIn. Cisco Networking Academy. 10+ years tenure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Shawn Hillard</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Manager, Network Operations</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Armstrong Group of Companies</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shawn-hillard-21509a37/</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP), pivot DWDM, TPM, DIMMs, pre-owned Cisco</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Existing HubSpot 539438. Day 1 2026-05-01. 3rd-degree LI. NOC manager 20 years tenure since 2006.</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I347"/>
+  <dimension ref="A1:I359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16606,6 +16606,565 @@
       <c r="I347" t="inlineStr">
         <is>
           <t>Existing HubSpot 539438. Day 1 2026-05-01. 3rd-degree LI. NOC manager 20 years tenure since 2006.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Rob Mikita</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Armstrong Group of Companies</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rob-mikita-7a2344116</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP wedge); MCTV integration hook</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>9.8yr Network Eng + 20+ yrs total. Restricted 3rd-deg LinkedIn, ZoomInfo FULL_MATCH 98%. Day 1 2026-05-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Lindsey Quinn</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Network Security Administrator</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Armstrong Group of Companies</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lindsey-q-5470ba71</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP wedge); Bayer DC Network background</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>6.5yr at Armstrong, prior Bayer Data Center Network Tech Analyst. Restricted 3rd-deg LinkedIn, ZoomInfo FULL_MATCH 99%. Day 1 2026-05-13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>John McArdle III</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Telecommunications Vendor Management</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Armstrong Group of Companies</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-mcardle-iii-16152254</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>DWDM pain-led; SmartOptics DCP wedge for MCTV interconnect</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>14+ yr Telecom Vendor Mgmt, 30+ yrs CLEC switching incl VarTec, McLeod USA, CapRock + AIT Director Eng Japan + US Navy. Highest-value Armstrong target. Day 1 2026-05-28 cooling gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Eric Aulbach</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Chief Information and Group Marketing Officer</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Armstrong Group of Companies</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ericaulbach</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Pain-led DWDM exec; MCTV close hook (96k passings OH+WV, Q2 2026)</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>CIO 14yr at Armstrong; 30+ yrs IT incl Marconi PLC InfoSec. MCTV definitive agreement Feb 17 2026 closes Q2. Person 6 Armstrong batch. Day 1 2026-06-03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Richard Laing</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>President &amp; Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Stellar Broadband</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-laing-42744a1</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Pain-led DWDM exec; transition hook (Spartan Net 22yr CIO to Stellar P&amp;COO Jan 2026)</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Just transitioned 2026-01-31 from Spartan Net CIO 22yr to Stellar President &amp; COO. Long network ops career (NOC, Director Net Ops, CIO). Person 1 Stellar batch. Day 1 2026-04-27. Note: Ryan Potter at Stellar owned by Brian Charrette (not JAM); flag account-request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Charles Kelley</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Corporate Network Administrator</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Patrick Industries</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/charles-kelley-b6b953116</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP wedge), TPM/DIMMs follow-on</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Existing Andy-owned HubSpot contact (lifecycle stale "customer" but no deals). 10mo cold. USMC IT Supervisor 2012-2016 background, then Patrick since 2016. Person 1 Patrick Industries batch. Day 1 2026-04-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>John Calder</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Director, Data Center Operations</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAAD7CH8BT5ajEAFsU0xbl4mG7TT6lJ9VlRQ,NAME_SEARCH,z7no</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-27. Shallow qualify (HubSpot 209780627792). 451 Research hook. Last contacted 2026-04-14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Aidan Rigney</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Vice President, Infrastructure &amp; Operations</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>TPM pain-led exec (8 to 12% SmartNet/ProSupport increases) + DWDM, DIMMs, optics</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-01. Ireland (Dunleer, Leinster). Shallow qualify (HubSpot 180505461638). EMEA infra angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Gregg Blauth</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Head of Global Network Services</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAAbK6eoBkBQFCL9h9XA1sxf90dxSwT7H4rI,NAME_SEARCH,mkBC</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-07. Princeton NJ. Shallow qualify (HubSpot 180505461635). 451 Research hook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Nicholas Kolchev</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Senior Network Administrator &amp; Engineer</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicholas-kolchev-49ab6961</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-13. Aurora CO. Shallow qualify (HubSpot 209783399847). ZoomInfo FULL_MATCH 94. Direct (303) 858-6469. Person 4 of S&amp;P batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Guruprasad Ramamoorthy</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Global Vice President, Head of Cloud &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/guruprasadramamoorthy</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>TPM pain-led exec (8 to 12% SmartNet/ProSupport increases) + DWDM, DIMMs, optics</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-19. NYC. Shallow qualify (HubSpot 180505461639). ZoomInfo FULL_MATCH 98. Direct (212) 438-3303. Last contacted 2025-12-11. VP-Level. Person 5 of S&amp;P batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Craig Suellentrop</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Director, Infrastructure Engineering &amp; Automation</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/craigsuellentrop</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-26. Englewood CO. Shallow qualify (HubSpot 7455113472). ZoomInfo FULL_MATCH 94. Email corrected ihsmarkit.com -&gt; spglobal.com. Direct (303) 858-6925. 24 mo stale (cold re-engagement). Person 6 of S&amp;P batch.</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I359"/>
+  <dimension ref="A1:I400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17165,6 +17165,1863 @@
       <c r="I359" t="inlineStr">
         <is>
           <t>Day 1 = 2026-05-26. Englewood CO. Shallow qualify (HubSpot 7455113472). ZoomInfo FULL_MATCH 94. Email corrected ihsmarkit.com -&gt; spglobal.com. Direct (303) 858-6925. 24 mo stale (cold re-engagement). Person 6 of S&amp;P batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Roni Goldstein</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>IT of Vendor Management Head</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roni-goldstein-77b991</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>TPM pain-led (8-12% SmartNet/ProSupport) + DWDM, DIMMs, SFP follow-on</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-06-02. NYC ET. Existing HubSpot 180505461636 (phone reconciled, LinkedIn added). ZoomInfo FULL_MATCH 98%. Email roni.goldstein@spglobal.com, direct (212) 438-3303, mobile (212) 438-1337. Last contacted 2025-12-11. Person 7 of S&amp;P batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>John Aker</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Chief Engineer</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Saddleback Communications</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-aker-31091043</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge (free SFP) + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-27. Scottsdale AZ MT. Existing HubSpot 415262 (jobtitle updated from IT Manager to Chief Engineer, mobile + LinkedIn added). ZoomInfo FULL_MATCH 95%. Email jaker@saddlebackcomm.com, direct (480) 362-7037, mobile (480) 577-0710. Saddleback JAM-owned co 9126599000 (50 employees, tribal-owned ISP Salt River Pima-Maricopa). Person 1 of new Saddleback batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>David Dahl</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Network Operations</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Saddleback Communications</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-dahl-39713440</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge (free SFP) + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-01. Scottsdale AZ MT. NEW HubSpot 217939783453 (created with full data + Saddleback association). ZoomInfo FULL_MATCH 94%. Email ddahl@saddlebackcomm.com, direct (480) 362-7108, mobile (480) 850-7000. 2nd-degree LinkedIn (mutual w/ Matthew Geesling). Person 2 of Saddleback batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Kevin Benson</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Saddleback Communications</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kevin-benson-1791829a/</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge (free SFP) + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-07. Scottsdale AZ MT. EXISTING HubSpot 114486966791 (phone reformatted, mobile + LinkedIn URL added). Email kevin@saddlebackcomm.com, direct +1 (480) 362-7040, mobile +1 (480) 577-0890. Carrier Services role. Saddleback JAM-owned co 9126599000 (50 employees, tribal-owned ISP Salt River Pima-Maricopa). Hook: 3,000+ fiber miles to core backbone. Person 3 of Saddleback batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>David Wildrick</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Switch Technician / VoIP Engineer</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Saddleback Communications</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-wildrick-ccna-40677933/</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge (free SFP) + Cisco SmartNet TPM E5 (CCNA bg), DIMMs, DWDM follow-on</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-13. Scottsdale AZ MT. NEW HubSpot 217952912281 (created with full data + Saddleback association). ZoomInfo FULL_MATCH 93. Email dwildrick@saddlebackcomm.com, direct +1 (480) 362-7027, mobile +1 (480) 845-4571. CCNA confirms Cisco environment. Hook: 3,000+ fiber miles + Cisco switching. Person 4 of Saddleback batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>James Caldwell</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Outside Plant Engineer</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Saddleback Communications</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-caldwell-17942490/</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge (free SFP) + DWDM open line E3 (OSP angle), DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-19. Scottsdale AZ MT. NEW HubSpot 217950599435 (created with full data + Saddleback association). ZoomInfo FULL_MATCH 93. Email jcaldwell@saddlebackcomm.com, direct +1 (480) 362-7071, mobile +1 (801) 259-5312. OSP role spec sees optics for new spans. Hook: 3,000+ fiber miles to core backbone. Person 5 of Saddleback batch (next person uses +10 BD cooling).</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Samuel Price</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Manager, Network Operations</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>360 Broadband</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samuel-price-2657141a5/</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge (free SFP) + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-27. Durant OK CT. EXISTING HubSpot 46493165834 (mobile + LinkedIn URL added). Email sprice@360broadband.com, mobile +1 (903) 449-8485. ZoomInfo FULL_MATCH 98. 360 Broadband JAM-owned co 21823752821 (50 employees, hybrid FTTH plus wireless ISP). Hook: CTO promotion of Christopher Buchanan (head of network ops). Person 1 of 360 Broadband batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Thad Prater</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>360 Broadband</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thad-prater-190907166/</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Network sample-offer wedge (free SFP) + DWDM, DIMMs, TPM follow-on</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-01. Durant OK CT (assumed HQ-based). NEW HubSpot 217957497784 (created with full data + 360 Broadband association). Email mprater@360broadband.com, mobile +1 (972) 375-5871. ZoomInfo FULL_MATCH 98. Hook: CTO promotion of Christopher Buchanan. Person 2 of 360 Broadband batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Troy Murphy</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Director, Procurement, Logistics &amp; Fleet</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>360 Broadband</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/troykmurphy/</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Pain-led TPM (Cisco SmartNet alternative) + DWDM, DIMMs, pre-owned Cisco/Juniper layered</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-07. Durant OK CT. EXISTING HubSpot 46493165831 (jobtitle updated, mobile + LinkedIn URL added). Email tmurphy@360broadband.com, mobile +1 (903) 819-1390. ZoomInfo FULL_MATCH 98. Procurement Director at 50 person ISP signs network gear POs. Hook: CTO promotion of Christopher Buchanan (vendor relationships re-evaluated under leadership change). Person 3 of 360 Broadband batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Joshua Nelson</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Vice President, Network Services</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Vero Networks</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/josh-nelson-bb375884</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP) Email 1, then TPM SmartNet + DIMMs layered</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-27 4pm. Boulder CO HQ; Joshua based Baker FL ET. EXISTING HubSpot 183790691372 (LinkedIn josh-nelson-bb375884 added, phone formatted). Email jnelson@veronetworks.com FULL_MATCH 98, mobile +1 (850) 490-0409 verified. VP Network Services since Dec 2024. FRESH HOOK: Vero closed Telephone Electronics Corp (TEC) acquisition April 14 2026, gained 4,500 mile fiber footprint MS+AL+TN, ~444K combined homes. Plus $500M Hamilton Lane/Braemont/Delta-v investment Feb 23. Optics standardization across acquired networks is the natural opener. Vero Networks stagger person 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Trenton McVicker</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Manager, Television &amp; Network Operations</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>OEC Fiber</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/trenton-mcvicker-4b286576</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP) Email 1, then SmartNet TPM + DIMMs layered</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-27 4pm. Norman OK CT. EXISTING HubSpot 46494059684 (LinkedIn URL added, mobile (405) 217-6786 added). Email trenton.mcvicker@oecfiber.com FULL_MATCH 98 ZoomInfo. In role since Feb 2022. Hook: OEC From the Top Jan 2026 update flagged fiber build leveling off, modest expansion aligned to electric side. Optics standardization is the opener. OEC Fiber stagger person 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Michael Thomas</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Senior Manager, Technology Services &amp; Network Operations</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>OEC Fiber</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Network sample-offer (free SFP) Email 1, then SmartNet TPM + DIMMs layered</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-01 4pm. OK CT. EXISTING HubSpot 46494059681 (direct +1 (405) 217-6781 and mobile +1 (405) 314-5675 verified via ZoomInfo, replaced corporate main). Email michael@oecfiber.com (HubSpot historic touch 2024-10-02 confirms valid). ZoomInfo FULL_MATCH 93 returned alt michael.tomas@okcoop.org against parent Oklahoma Electric Cooperative co; HubSpot oecfiber.com retained. ZoomInfo title Manager Network Operations, HubSpot Senior Manager TS+NetOps; HubSpot title used. In seat since 2018, 7 plus year tenure. Hook: OEC Jan 2026 update flagged fiber build leveling off. OEC Fiber stagger person 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Joe Torres</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Senior Manager of Outside Plant and Fiber Technicians</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>OEC Fiber</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Network sample-offer (SFP) Email 1, then SmartOptics DWDM, then Cisco refurb + multi-vendor TPM</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-07 4pm. OK CT. HubSpot 46494059683. Email joe@oecfiber.com (HubSpot historic touch 2024-10-02 valid). Phone (405) 217-6678 from HubSpot. ZoomInfo skipped (email + phone present, mobile not critical). HubSpot shallow qualify path. Hook: OEC Fiber hit 40,000 fiber subs, only third co-op nationally at that scale (April 2026 CEO update). OEC Fiber stagger person 3, last_day1 2026-05-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>David Godspeed</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>OEC Fiber</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>DWDM/SmartOptics economics Email 1, then SFP sample, OEM maintenance, DIMMs</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-14 4pm. HubSpot 51212375443. Email david@oecfiber.com (HubSpot historic touch 2024-10-02 valid). No phone in HubSpot, ZoomInfo skipped (President, sequence is email-only). HubSpot shallow qualify path. Hook: OEC Fiber hit 40,000 fiber subs (April 2026 CEO update). OEC Fiber stagger person 4, last_day1 2026-05-14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Devin Eads</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Fidelity Communications</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Network sample-offer (SFP) Email 1, then DWDM, TPM (Cisco SmartNet), DIMMs</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-27 4pm. HubSpot 183789739951. Email devin.eads@fidelitycommunications.com (legacy domain still live post-Sparklight rebrand). Phone (573) 468-1202, mobile (573) 619-9882, all populated. ZoomInfo skipped. HubSpot shallow qualify path. Cable One/Sparklight (acq 2019, rebrand 2024). Fidelity Communications stagger person 1, last_day1 2026-04-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Jason Bell</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Fidelity Communications</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Network sample-offer (SFP) Email 1, then DWDM, TPM (Cisco/Juniper), DIMMs</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-01 4pm. HubSpot contactId 564304. Email jason.bell@fidelitycommunications.com (Sparklight subsidiary domain still live). Phone (573) 468-8081, mobile (573) 468-1043. Last touched 2025-06-12, ~10mo cold. Hook: Fidelity rebuilding fiber in Buffalo and Adrian, MO. ZoomInfo skipped (HubSpot complete). HubSpot shallow qualify path. Stagger person 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Michael Gorzik</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Supervisor II, NOC Tier</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Fidelity Communications</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Network sample-offer (SFP) Email 1, then TPM, DWDM, DIMMs</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-07 4pm. HubSpot contactId 563292. Email mike.gorzik@fidelitycommunications.com. Phone (573) 468-8081, mobile (573) 468-1024. Last touched 2025-06-12, ~10mo cold. NOC supervisor owns replacement optics. Hook: Fidelity fiber rebuild Buffalo/Adrian. HubSpot shallow qualify path. Stagger person 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Braden Hylton</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Network Operations Supervisor</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Fidelity Communications</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Network sample-offer (SFP) Email 1, then DWDM, TPM, DIMMs</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-13 4pm. HubSpot contactId 383763. Email braden@fidnet.com (legacy Fidelity domain pre-Sparklight rebrand, last touched 2025-01-13). Phone 5734688081. Lifecyclestage SQL, ~15mo cold. Re-engagement on known target. Hook: Fidelity fiber rebuild Buffalo/Adrian. ADMIN FLAG: verify fidnet.com domain before 2026-05-13 send. HubSpot shallow qualify path. Stagger person 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Chad Johnston</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>OSP Engineer</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Fidelity Communications</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Network sample-offer (SFP) Email 1, then DWDM, TPM (Cisco/Juniper), DIMMs</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-19 4pm. HubSpot contactId 383520. Email chad.johnston@fidelitycommunications.com. Phone +1 (573) 468-1035. SQL stage, last touched 2024-08-09, ~20mo cold. Hook: Fidelity fiber rebuild Buffalo/Adrian. OSP role = closest to fiber plant + transceivers. HubSpot shallow qualify path. Stagger person 5 (cooling gap applied).</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>John DeBroeck</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Fidelity Communications</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Network sample-offer (SFP) Email 1, then DWDM, TPM (Cisco/Juniper), DIMMs</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-06-03 4pm. HubSpot contactId 383905. Email john.debroeck@fidelitycommunications.com. Phone +1 (574) 468-1236. SQL stage, last touched 2025-06-06, ~10mo cold. Title generic in HubSpot (just 'Engineer') but team-curated SQL at cable MSO. Hook: Fidelity fiber rebuild Buffalo/Adrian. FLAG: confirm exact discipline on first live touch. HubSpot shallow qualify path. Stagger person 6 (+10bd cooling from person 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Ron Bauer</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Vero Networks</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Pain-led TPM Email 1, then DWDM (transport), DIMMs, pre owned switching, close</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-01 4pm. HubSpot contactId 146559768632. Email rbauer@veronetworks.com. Phone +1 (303) 350-4060 (Denver area). Mobile field has malformed +57 country code data, leaving as is. Director of IT at Vero (FTTP carrier). Hook: TEC acquisition closed 2026-04-15 + $500M FTTP investment Feb 2026. HubSpot shallow qualify path. Stagger person 2 at Vero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Neil Bryan</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Director of District Network Services for IN, IL, MO</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Vero Networks</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Sample SFP optics wedge Email 1, then optics lead time, DIMMs and TPM layered</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-08 4pm. HubSpot contactId 1105301. Email nbryan@veronetworks.com. Phone (303) 350-4060. Mobile (585) 350-9661. Last contacted 2023-04-25 (~3 yrs cold). Director of District Network Services for IN, IL, MO at Vero (FTTP carrier). Hook: TEC acquisition closed 2026-04-15 (~4,500 fiber miles MS AL TN), $500M raise Feb 2026, BendTel close Dec 2025. Re-engagement angle. Strategy note 108697233988, LINKED_IN_CONNECT 108697175374. HubSpot shallow qualify. Vero Networks stagger person 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Nathan McGinn</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Senior VP, Operations</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Vero Networks</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Pain-led lead time + capex stretch Email 1, then DWDM Smartoptics DCP, DIMMs and TPM</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-22 4pm. HubSpot contactId 1028901. Email nmcginn@veronetworks.com. Phone +1 (303) 241-0787. Never contacted (clean slate). SVP Operations at Vero (FTTP carrier). Sells on lead time and capex stretch, not optics specifics. Hook: TEC close 2026-04-15 + BendTel close Dec 2025 + $500M raise Feb 2026. Strategy note 108704469901, LINKED_IN_CONNECT 108692803639. HubSpot shallow qualify. Vero Networks stagger person 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Dave Jones</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Vero Networks</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Pain-led DWDM transport architecture Email 1, then 400G upgrade path, pre owned and TPM</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-06-12 4pm. HubSpot contactId 567830. Email djones@veronetworks.com. Phone (303) 350-4060. Mobile (303) 350-4060 ext. 110. ACTIVE-SEQUENCE FILTER PASSED: single OSI email sent 2026-03-18 (Reconnecting on Smartoptics), no follow-up activity in 38 days, queue clean. Not an active sequence. CTO at Vero (FTTP carrier), highest-value Vero contact, owns transport architecture. Hook: TEC close 2026-04-15 + $500M raise Feb 2026. Strategy note 108704206601, LINKED_IN_CONNECT 108704461904. HubSpot shallow qualify. Vero Networks stagger person 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Chadd Giles</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer &amp; Founding Partner</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chadd-giles-853b7536/</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1, then optics lead time on the 8-state buildout, then DWDM Smartoptics DCP for transport between markets</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-27 4pm. HubSpot contactId 46494210911 (existing, owned by inactive Ramon Wu, permission denied for property updates; admin flag in strategy note). Email chadd@resoundnetworks.com. Mobile +1 (806) 662-8615. CTO/Founder at 51-person rural ISP, 30+ yrs telecom (Verizon System Performance Engineer 2006-2016, Sprint, AT&amp;T, Dobson). Hook: gaiia OSS/BSS go-live Feb 5 2026, eight-state expansion to ~5M homes, ISP acquisitions push. Strategy note 108697255235, LINKED_IN_CONNECT 108704573611. Resound Networks stagger person 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Chris Vainrib</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Director, Radio Frequency Engineering &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-vainrib-b5681014/</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1, then Smartoptics DCP for transport, then pre owned Cisco/Juniper for spares and edge</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-01 4pm. NEW HubSpot contactId 218024429137 (created with full data + Resound co association). Email chris.vainrib@resoundnetworks.com. Mobile +1 (832) 580-6523. Director at Resound since Jan 2024, in seat since Dec 2019. 30+ yrs vendor + operator background: ERF Wireless senior RF engineer, Firetide systems engineering manager, Ruckus Wireless, Aerohive, US Army MSE transmission. Owns transport conversation. Hook: gaiia go-live Feb 2026, eight-state expansion. Strategy note 108697338951, LINKED_IN_CONNECT 108704575882. Resound Networks stagger person 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Jay Kapadia</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Manager, Network Engineering</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kapadiajay/</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1, then optics lead time on the 8-state buildout, then server memory + TPM for the network team</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-07 4pm. NEW HubSpot contactId 218024149674 (created with full data + Resound co association). Email jay@resoundnetworks.com. Mobile +1 (806) 662-0620. Manager Network Engineering at Resound since June 2023; in seat at Resound since Aug 2017 (8+ yrs at one ISP). Strong operational influence on network gear selection. Hook: gaiia go-live Feb 2026, eight-state expansion. Strategy note 108697291560, LINKED_IN_CONNECT 108704566646. Resound Networks stagger person 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Cole Giles</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>VP-Wireless Infrastructure</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cole-giles-901381177/</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Network sample SFP -&gt; SmartOptics DCP DWDM -&gt; DDR4 DIMMs / Pre owned</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Day 1 2026-05-13 4pm. Stagger Resound person 4. ZoomInfo email + mobile. New HubSpot contact 218030503269.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Chintan Mehta</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chintanrashmikantmehta/</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Network sample SFP -&gt; DWDM (StackPath edge background) -&gt; DIMMs / Pre owned</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Andy (existing)</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Day 1 2026-05-28 4pm (cooling gap, person 5). Existing HubSpot 46500566424; mobile updated, phone cleared (was company main), city/state/LinkedIn URL added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Luke Hutchins</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luke-hutchins-51724818a/</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Network sample SFP -&gt; Pre owned routing (WISP background) -&gt; DWDM -&gt; DIMMs</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Day 1 2026-06-03 4pm. Stagger Resound person 6. 3rd degree restricted profile but ZoomInfo full match. New HubSpot contact 217946540573.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Jorge Renteria Jr</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-renteria-jr-a27848205/</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1, then optics lead time on the 8-state buildout, then pre owned Cisco/Juniper for spares</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-06-09 4pm. NEW HubSpot contactId 218041038187. Email jorge.renteria@resoundnetworks.com. Mobile +1 (806) 664-7960. Network Engineer since May 2025 (just promoted from NOC operator; was Tier 2 Tech Support before that). 4-5 yrs experience, all at Resound. Strategy note 108697864105, LINKED_IN_CONNECT 108705105751. Resound Networks stagger person 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Chad Staggs</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chad-staggs-831b8283/</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1, then HPE TAC + TPM hook (pre owned Cisco/Juniper, third party maintenance), then optics lead time</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-06-15 4pm. Existing HubSpot contactId 46500566423 (owned by inactive Ramon Wu — admin flag in strategy note for ownership re-assignment). Email chad.staggs@resoundnetworks.com. Mobile +1 (870) 826-1505. Network Engineer at Resound since June 2023; prior 10 yrs Telecom Network Admin at Townes Tele-Communications + 2 yrs HPE TAC. 15-19 yrs experience. HPE TAC background = pre owned + TPM angle should resonate. Strategy note 108697915915, LINKED_IN_CONNECT 108697931668. Resound Networks stagger person 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Bob Hancock</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Director, Network Architecture</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Momentum Telecom</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bob-hancock-2a85a519/</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1 (he reposts Community IX DWDM upgrades and NANOG content), then DWDM tied to Horizon Telecom integration, then DIMMs core compute, then Cisco/Juniper TPM</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-04-28 4pm. Re-qualification of shallow-path candidate under fixed full-LinkedIn-read rule. HubSpot contact 185747801241 (already owned by Andy). Email bhancock@momentumtelecom.com. Mobile (205) 261-8402. Direct (205) 978-6027. Gardendale AL. 1st-degree (prior LINKED_IN_CONNECT 107906611224 completed and accepted 2026-04). New strategy note 108700976527 supersedes prior 107906359178 (TPM-led was wrong angle; activity feed says optics/DWDM). New LINKED_IN_CONNECT 108700888963 due 2026-04-28. Momentum Telecom stagger person 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>David Christian</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Senior Director, Network Access &amp; Process Optimization</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Momentum Telecom</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-christian-687ba245/</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1, then DWDM transport for Horizon integration, then DIMMs across 65 DCs, then multi vendor TPM</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-04 4pm. Re-qualification of shallow-path candidate. HubSpot contact 185747801236 (Andy owned). Email david.christian@momentumtelecom.com. Mobile (423) 579-5685. Direct (423) 797-6306. Bristol TN. 1st-degree (mutual John, likely John Houston). Career: Point Broadband sales BD -&gt; Momentum PM Solution -&gt; Director Network Solutions -&gt; Sr Director. TheOrg bio confirms 65 DC scope on data and cloud network access (AWS/Azure). Strategy note 108700886965, LINKED_IN_CONNECT 108708558602. Momentum Telecom stagger person 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Justin Morse</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Network Solutions Architect</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Momentum Telecom</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/morsej/</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge Email 1, then DWDM Horizon integration, then pre owned Juniper and Arista (his cert stack), then Cisco/Juniper TPM</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Pursue</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Day 1 = 2026-05-08 4pm. Re-qualification of shallow-path candidate. HubSpot contact 200671002919 (Andy owned). Email justin.morse@momentumtelecom.com. Mobile (832) 752-6448. Bay Village OH (corrected from Rocky River). 1st-degree (mutuals Ryan, Jason). Pure technical career: COOP -&gt; field tech -&gt; network engineer -&gt; Senior NE -&gt; Solutions Architect (3+ yrs). Cert run last 12 months: Juniper JNCIA-MistAI, JNCIS-MistAI-Wireless, JSDWAN, Arista ACE L1, Cato Distinguished Support Associate. Strategy note 108701001293, LINKED_IN_CONNECT 108708448888. ADMIN: cleared bad phone (was Momentum main toll-free 877-251-5554), retained mobile. Momentum Telecom stagger person 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Tyler Collen</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Momentum Telecom</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tyler-collen-26a428163/</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge then DWDM Horizon integration then DIMMs then TPM</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>6 emails queued, LI connect task due 5/14, strategy note 108701328184</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Path B ZoomInfo FULL_MATCH 98%. 11 yr internal Momentum arc NOC to Systems to Network. Day 1 2026-05-14. Stagger person 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Keith Perkins</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Momentum Telecom</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/keith-perkins-13176726b/</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge then DWDM Horizon integration then DIMMs then TPM</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>6 emails queued, LI connect task due 5/29, strategy note 108710703232</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Path B ZoomInfo FULL_MATCH 95%. Prior Point Broadband NE 2016-2019. Day 1 2026-05-29 (cooling gap person 5). John Houston LinkedIn mutual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Azri Cooper</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Momentum Telecom</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Sample SFP wedge then DWDM Horizon integration then DIMMs then TPM</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Updated</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>6 emails queued, LI connect task due 6/4, strategy note 108710544479</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Path B ZoomInfo FULL_MATCH 94%. 20-29 yrs exp, prior Weather Channel Ops Eng. LinkedIn /in/ not findable. Day 1 2026-06-04 stagger person 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Steve Beach</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Manager, NOC</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Midco</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/steve-beach-59000a61</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SmartOptics SFP wedge)</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>JAM Andy</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Sequence queued, Day1 2026-06-22</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Midco Fiber Forward $43M Sioux Falls + $9.1M Bismarck Mandan; 25yr Midco lifer; HS 190542957394</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Brian Beck</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Manager, Network Capacity</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Midco</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brian-beck-17951a83</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SmartOptics SFP wedge)</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>JAM Andy</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Sequence queued, Day1 2026-06-26</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>32yr Midco lifer joined 1993; capacity planning audience for Fiber Forward; HS 190542957398</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Miles McCredie</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Core IP Principal Network Engineer II</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Midco</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miles-mccredie</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SmartOptics SFP wedge)</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>JAM Andy</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Sequence queued, Day1 2026-07-02</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>4yr in role / 30+yr exp; core IP focus, 400G transport angle; HS 140606145562</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prospects" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Status" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unenrolled" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies Prospected" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$I$1</definedName>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +56,18 @@
       <name val="Arial"/>
       <color rgb="00444444"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -83,8 +94,18 @@
         <fgColor rgb="00833C00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -92,11 +113,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -113,6 +148,21 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I400"/>
+  <dimension ref="A1:I405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19022,6 +19072,241 @@
       <c r="I400" t="inlineStr">
         <is>
           <t>4yr in role / 30+yr exp; core IP focus, 400G transport angle; HS 140606145562</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Mason Moesch</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineering Manager</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Nsight</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/masonmoesch/</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM (NetApp)</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Contact exists (ID 102931114785)</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>6-email sequence queued, Email 1: 2026-05-04</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Promoted Feb 2026, follows NetApp on LinkedIn, Backup Solutions skill. ZI FULL_MATCH. Regional carrier WI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Peter Whiteside</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Vice President of Infrastructure</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Brivo</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-whiteside-1b490311/</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>TPM/multi-vendor maintenance (merger hook)</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>New contact created (ID 219246525852)</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>6-email sequence queued, Email 1: 2026-05-04</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Eagle Eye + Brivo merger Dec 2025. Inherited two infra stacks. ZI COMPANY_ONLY_MATCH; email pattern-inferred from brivo.com confirmed contacts. LinkedIn Path A verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Mitch Vieu</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Senior Manager Telecom Engineering and Operations</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Copper Valley Telephone Cooperative</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/mitch-vieu-b785a810b/</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Pain-Led DWDM: rural Alaska carrier, OSP + network engineering, budget owner. TPM, Pre-Owned, Optics follow-ups.</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>In sequence</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>6-email Pain-Led DWDM sequence queued. Day 1: 2026-05-04.</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Prior OSI engagement Oct 2023. Last contact 2.5 yrs cold. HubSpot ID 2844251.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Robert Geraghty</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Lead Network Engineer</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Copper Valley Telephone Cooperative</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/robert-geraghty-b72b9b19b/</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network: optical specialist running 400G DWDM/EDFA at CVTC. Secondary: DWDM supply chain, TPM, Pre-Owned.</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>In sequence</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>6-email Sample-Offer Network sequence queued. Day 1: 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Certified Optical Network Engineer cert Sep 2025. Built CVTC ISP (ASN:20259). Prior OSI LI contact Jan 2024. HubSpot ID 127508779633.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Tim Chin</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Director of IT &amp; Security</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Rajant Corp</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tim-chin-rajant/</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>TPM (SmartNet savings, Cisco support), DIMMs/compute, spare optics for field nodes</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>6-email sequence queued (Pain-Led TPM). LinkedIn connect due 2026-05-05.</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>DoD contractor, Breadcrumb mesh nodes. Cost-reduction focus (27% savings on profile). Park Place/SE merger angle for E2.</t>
         </is>
       </c>
     </row>
@@ -20657,4 +20942,1230 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Last Sequence Date</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Midco</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Vero Networks</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Hunter Communications</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Consumer Cellular</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Resound Networks</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Midcontinent Communications, Inc.</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Rackspace</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Momentum Telecom</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Armstrong Group of Companies</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Fidelity Communications</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>altafiber</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Saddleback Communications</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Cantor Fitzgerald</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Fatbeam</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>OEC Fiber</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Patrick Industries</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Axcent Networks</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Copper Valley Telephone Cooperative</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>BNY Mellon</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Lingo Communications</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>360 Broadband</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Princeton University</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Rajant</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Armstrong Group</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Altafiber</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>North American Interconnect</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Nsight</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Consolidated Telcom</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Desjardins</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Visionary Broadband</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Brivo</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Stellar Broadband</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Grande Communications</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Thor Industries</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Bergen New Bridge Medical Center</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>SBA Communications</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>DFA Milk</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Transaction Network Services</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Atlantic Health Systems</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>Global Cloud Xchange</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Baxter International</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Winnebago Industries</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>Skywire Networks</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Spectrotel</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>VTX1 Companies</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Docomo Pacific</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>LG CNS</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Hurricane Electric</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>Big River Communications</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>SiFi Networks</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>MetTel</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Bell Canada</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>GVTC Communications</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Dark Fiber and Infrastructure</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>Sabey Data Centers</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Astound Broadband</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>Arvig</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>EastLink</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>LFT Fiber</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>Plateau Telecommunications</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>Nitel</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>ITHAKA</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>Bausch Health</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>KeyBank</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>BullsEye Telecom</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>Netceed US</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>Lippert</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>email-queue.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I405"/>
+  <dimension ref="A1:I409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19307,6 +19307,194 @@
       <c r="I405" t="inlineStr">
         <is>
           <t>DoD contractor, Breadcrumb mesh nodes. Cost-reduction focus (27% savings on profile). Park Place/SE merger angle for E2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Girish Budibetta</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Global Lead for Data Center Transformation</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/girish-budibetta-bb52015/</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMMs), TPM, Optics, DWDM</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Sequence queued Day 1 2026-05-29</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>19+ yrs DC transformation, AWS partnership expansion, approved vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Gregory Perez</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Director of Data Center Operations</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gregoryperez-nfl</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM (NetApp/Cisco) + Storage</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Active - Sequence Started</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Sequence queued E1 2026-05-06</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Email: perezg@nfl.com (ZI 98% alt pattern). NFL+Azure AI fresh hook. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Douglas Neu</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>VP of Technology</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/douglas-neu</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMMs/Compute) + Optics</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Active - Sequence Started</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Sequence queued E1 2026-05-12</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Email: douglas.neu@nfl.com (dominant-pattern, no ZI match - monitor for bounce). Kubernetes/compute hook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Trey Dillen</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Sr. Director of Technology - NFL Films</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/trey-dillen</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SFPs/Optics) + DWDM</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Active - Sequence Started</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Sequence queued E1 2026-05-18</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Email: trey.dillen@nfl.com (ZI confirmed). NFL Films 9 intl productions fresh hook. Career trajectory hook.</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -7,13 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prospects" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Status" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unenrolled" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies Prospected" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tab1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prospects" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Status" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unenrolled" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Companies Prospected" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do Not Auto-Prospect" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prospects'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prospects'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,7 +69,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +106,12 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -163,6 +171,11 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,7 +541,7468 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I409"/>
+  <dimension ref="A2:K170"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LinkedIn URL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OSI Angle</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>HubSpot Status</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Date Added</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stuart Paulsen</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VP Network</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Instinet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stuart-paulsen-579a97/</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220073047971)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>VP Network since Oct 1994 (31 yrs). EE + Columbia MBA. ZI match 98%. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bennett Sciacca</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Procurement Operations</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bennettsciacca/</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sr. Manager Procurement Operations at NFL (Apr 2025). 10yrs NY Mets procurement. ZI FULL_MATCH 95. Email: bsciacca@nfl.com (nonstandard). HubSpot ID 220073121653. Day 1=2026-08-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Steven Lee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VP | System Administrator | Citrix Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Instinet</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAACSa8cBrDQKQZ4DLBLN_6LNDp_8iTckAls</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMMs)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220078365608)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-20</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>21yr Citrix/Windows SysAdmin. ZI limit hit, email derived from pattern. dominant-pattern. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>William Figlyar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sr. Unix/Linux Administrator VP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Instinet</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAAynKdYBVlrErJI_BZtzbGEyWvkoFYWXVcI,NAME_SEARCH,3JOO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sample-Offer Compute (DIMMs)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220079714743)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-27</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>27yr Linux/Unix admin. Data Center (21), DR (9) skills. ZI limit hit, email derived from pattern. dominant-pattern. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aliuddin Ahmad</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data Center Support Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Instinet</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAA8B8TUBCt3IeMVQBcU8v8cHSEWD26V1bfU,NAME_SEARCH,P60m</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sample-Offer Compute (DIMMs)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220078990664)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-06-03</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30yr DC support, trading systems hardware. ZI limit, dominant-pattern email. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Michael Huang</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer, VP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Instinet</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAAIOFWgBPwWFzUVyGimetFyK8cH2NNKaSLo,NAME_SEARCH,-mmo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sample-Offer Optics</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Existing HubSpot contact (ID: 148963950725) - updated to IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-06-09</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Network Architect, low latency financial services, 4yr at Instinet. Cisco, Data Center skills. Procurement in prior role. Strong ICP. hubspot-existing email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Leo Pang</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Manager of Network Engineering, VP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The D.E. Shaw Group</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leo-pang-abb19a13/</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Contact updated (ID: 450077)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-08</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20+ yr network architect. Bloomberg (23 yrs), Jane Street (market data network), D.E. Shaw since Feb 2022. Email: leo.pang@deshaw.com (dominant pattern). 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Michael Hernandez</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vice President of Infrastructure Development</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The D.E. Shaw Group</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mhernandezit/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220347633245)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VP Infra Dev. Tech stack: Arista, Cisco Nexus 9k, BGP, VRF, OSPF. Previous: Highbridge Capital, Moody's. Email: michael.hernandez@deshaw.com (dominant pattern).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jacqueline Andrade</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Network Reliability</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>The D.E. Shaw Group</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jacqueline-ap/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220348099745)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-20</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NRE at D.E. Shaw (Jul 2022). Bloomberg LP network (3 yrs), ExterNetworks. NYC Metro. Email: jacqueline.andrade@deshaw.com (dominant pattern).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nitin Sharma</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vice President, Network Engineering</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The D.E. Shaw Group</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/nitinics/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220369705805)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Day 1: 2026-05-27. Cox carrier NE background (MPLS/BGP). dominant-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Joseph Cosaluzzo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Network Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The D. E. Shaw Group</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/josephcosaluzzo/</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220350122560)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Day 1: 2026-06-02. NYU Poly engineering. NRE at quant hedge fund. dominant-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Camilo Rojas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SVP IT Infrastructure - Network</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Citco</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/camilojrojas/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Existing HubSpot contact (ID: 323150)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Day 1: 2026-05-11. SVP level, heads network infra at global fund admin. hubspot-primary email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stuart London</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Head of IT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Citco Group Limited</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/stuartlondon/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220344842618)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Day 1: 2026-05-15. Head of IT, global fund admin. derived-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ray Chow</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Datacenter Manager</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Citco</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/ray-chow-32314b1/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Existing HubSpot contact (ID: 323492)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Day 1: 2026-05-21. DC Manager overseeing infra vendors, NJ. hubspot-primary email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Michael Mendes</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Citco</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/michael-mendes-31940229/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220338138764)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Day 1: 2026-05-28. Network Eng, Cisco Nexus/enterprise switching. Open to work but currently at Citco. derived-pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Frank Miles</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wilmington Trust Company</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/frank-miles-3634227/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 220369733048)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Day 1: 2026-05-11. Infrastructure Eng at financial services firm. derived-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Eric DeFoe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Network Administrator</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Epson Portland Inc</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>eric.defoe@epson.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hillsboro, OR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Transceivers / TPM / Compute</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/eric-defoe-7145719/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Email pattern UNVERIFIED (derived)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Scott Sams</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AVP Global Network Operations</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>scott.sams@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Transceivers / DWDM / Compute</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/scottjsams</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Existing HubSpot record (ID 552053) - title updated</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Matt Guzman</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Global Network Engineer IV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>matt.guzman@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Transceivers / DWDM / Compute</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/mattguzman/</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Argha Das</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Global Network Engineer IV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>argha.das@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mansfield, TX</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Transceivers / DWDM / Compute</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/argha-das-88307516/</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Robert Alvarado</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Global Network Engineer III</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>robert.alvarado@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Transceivers / DWDM / Compute</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/robert-alvarado-2327547b/</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Yousuf Arif</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Senior Network &amp; Security Engineer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>yousuf.arif@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Transceivers / DWDM / Compute</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/yousuf-arif-56a82b341/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Existing HubSpot record (ID 150187154217) - email added</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Todd Smith</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Global Network &amp; Voice Services Manager</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>todd.smith@us.abb.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Memphis, TN area</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Transceivers / DWDM / TPM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/todd-smith-17b239115/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Existing HubSpot ID 159833272841 - title updated from Network Manager</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Roger Gattis</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Director of Infrastructure &amp; Cloud Services</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ABB Motors and Mechanical</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>roger.gattis@us.abb.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fort Smith, AR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TPM / Transceivers / Compute</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/roger-gattis-2b074b63/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Existing HubSpot ID 159822109778 - title updated from ISDC Manager</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kent Kuckelman</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NOC Supervisor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Blue Valley Tele-Communications</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Network (Optics sample; DWDM + Pre-owned + TPM follow)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>E1 May 8 4pm; email: kentk@ (hubspot-existing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Karron Swift</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Blue Valley Tele-Communications</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAA6XV6gBjQfYKYzkgLwBp-mZ6cgGVyGK7JU,NAME_SEARCH,mU2h</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Network (Optics sample; TPM + DIMMs + Pre-owned follow)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>E1 May 14 4pm; email: kswift@ (dominant-pattern); VMware 7 entities hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gary Sparling</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Blue Valley Tele-Communications</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TPM Pain-Led (Optics + DIMMs + Pre-owned follow)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>E1 May 20 4pm; email: gsparling@ (dominant-pattern); BVT WiFi expansion hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>David Bratton</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VP Security and Networking</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Congruex</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dbratto/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Network (Sample-Offer optics; TPM + Used gear + DIMMs follow)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>E1 May 11 4pm; email: david@congruex.com (hubspot-existing); repost on risk/cost debates hook; Congruex OVE acquisition fresh hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rob Reynolds</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CIO and Emerging Technologies</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Congruex</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reynoldsrob/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TPM Pain-Led (Optics sample + DIMMs + Used gear follow)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>6-email sequence queued</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>E1 May 15 4pm; email: rob@congruex.com (hubspot-existing); AI cybersecurity post hook; Congruex OVE acquisition fresh hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ming Ikehara</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mingikehara</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 52772903848)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pending hook - LI task created 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Last contacted Sep 2024 (eligible). Redwood City CA, Cal Poly Pomona. LinkedIn gated. Need hook before E1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Steven Godfrey</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Manager, Infrastructure</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/steven-godfrey-84828555</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>New contact (ID: 221232756839)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pending hook - LI task created 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Strongest internal-buyer title at NEC. Rancho Cordova CA, Premium member. LinkedIn gated. Need hook before E1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Nagharaj Kamatchireddiar</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nagharaj-kamatchireddiar-6a95b6</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>New contact (ID: 221220127824)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pending hook - LI task created 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Plano TX. ZI acc 91. Prior OpenText record stale. LinkedIn nearly empty (1 conn). Email may need truncation check if bounce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Anthony Delanko</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>New contact (ID: 221232237378)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pending hook - LI task created 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Halethorpe MD. ZI acc 88. LinkedIn snippet only. No profile detail accessible. Need hook before E1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ivan Torres</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Director, IT Infrastructure &amp; Operations</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JMA Wireless</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 59315449907)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Director IT Infra &amp; Ops. ZI OPT_OUT, restricted profile. Fresh hook: $44M CHIPS Act funding for 5G O-RAN manufacturing expansion. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kristopher Rich</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AVP, IT Service Delivery</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>JMA Wireless</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 66129146027)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AVP IT Service Delivery. ZI accuracy 79, no prior contact. Fresh hook: $44M CHIPS Act funding. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Spencer Updike</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>IT Network Engineer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JMA Wireless</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 59315449904)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>IT Network Engineer. LinkedIn profile not publicly searchable. Fresh hook: $44M CHIPS Act manufacturing expansion. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Michael Cuyler</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>JMA Wireless</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 59315449910)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Promoted from NOC Analyst II to Infrastructure Engineer (ZI Feb 2026). Title updated in HubSpot. Fresh hook: $44M CHIPS Act expansion. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ming Ikehara</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Existing contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Existing HubSpot contact (Aug 2024, cold since Sep 2024). LinkedIn gated. Company-level hook: NEC IT services + CSG acquisition. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Steven Godfrey</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Manager, Infrastructure</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | Compute/DIMMs</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>New contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Strongest buyer title at NEC (mgr-level, internal infra oversight). LinkedIn gated. Company-level hook: NEC IT services + CSG acquisition. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Nagharaj Kamatchireddiar</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>New contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-26</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Prior HubSpot record at OpenText (stale). New NEC record created. LinkedIn nearly empty. Company-level hook: NEC CSG acquisition. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Anthony Delanko</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>New contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-01</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LinkedIn gated. Company-level hook: NEC IT services volume. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Kevin Parsons</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Senior Networking Engineer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>New contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>LinkedIn confirmed via search (Colorado Springs CO). Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Vito Passalacqua</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>New contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LinkedIn confirmed via search (Old Bridge NJ). Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Alex Burrell</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Existing contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-26</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>In HubSpot since Sep 2025, never outreached. Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chad Nelson</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Manager, IT Network</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Pain-Led</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Existing contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-01</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Manager level - stronger buyer angle. Last contacted Sep 2024. Sales Nav browser rendered no cards. Company-level hook: Black Box networking push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Akhilesh Sharma</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Existing contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-05</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Last contacted Sep 2024. Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jason Westermeyer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Existing contact - Sequenced</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-22</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Last contacted Sep 2024. Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. Cooling gap applied (6th person). 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Gary Lane</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Director, Infrastructure Engineering</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fifth Third Bank</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>gary.lane@53.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/gary-lane-326747b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Brad Chamberlain</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>VP - Director of Network Engineering</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fifth Third Bank</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>brad.chamberlain@53.com</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/brad-chamberlain-76a74211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jeffrey Zupp</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Principal Network Engineer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fifth Third Bank</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jeffrey.zupp@53.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/jeff-zupp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mike Mullins</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>VP IT Operations Technology</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fifth Third Bank</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mike.mullins@53.com</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/mike-mullins-3b03b12/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tracy Ross</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Lead Network Engineer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Fifth Third Bank</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>tracy.ross@53.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/tracy-ross-6515274/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ylli Agolli</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>VP, Network Architecture and Engineering Group</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>yagolli@us.mufg.jp</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/ylli-agolli-8b596185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Vincent Lobaccaro</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>VP Technology Infrastructure &amp; Operations</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>vlobaccaro@us.mufg.jp</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/vincent-lobaccaro-1489455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Bruce Frank</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Director, ITSM Command &amp; Data Center Operations</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>bfrank@us.mufg.jp</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/bruce-frank-ny/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Tayler Burley</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Director, IT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>IntelePeer</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>tburley@intelepeer.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/haveyoutriedturningitoffandonagain/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Julius Pasion</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Vice President, Systems Development</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IntelePeer</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jpasion@intelepeer.com</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Rolando Perez-Martinez</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Director, DevOps &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IntelePeer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>rperez@intelepeer.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/rolandoperezm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Justin Bewley</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SVP, System Architect &amp; DMS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IntelePeer</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jbewley@intelepeer.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/justin-bewley-1464331/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Juan Vento</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>VP of Engineering</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IntelePeer</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>jvento@intelepeer.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/juan-vento/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Samuel McReady</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Director, Head of Network Operations</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>samuel.mcready@ice.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/samuel-mcready/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Joseph Parker</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Vice President, Network &amp; Cloud Services</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>joseph.parker@ice.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/joseph-parker-892b84b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Craig Serritella</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Senior Director, Information Technology</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>craig.serritella@ice.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/craigers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Eric Lancaster</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Senior Data Center Engineer</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>eric.lancaster@ice.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/eric-lancaster-20b01519/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Neptali Anchundia</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Data Center Analyst</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>neptali.anchundia@theice.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>hubspot-primary</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/neptali-anchundia-2300a43/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mario Boutin</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sr. Director Infrastructure Telecom &amp; Ops</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>mario.boutin@prattwhitney.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mario-boutin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dick Lee</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Director Global Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>dick.lee@prattwhitney.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dick-lee/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Vanessa LaPierre-Cudnik</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Associate Director Network Operations</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>vanessa.lapierre-cudnik@prattwhitney.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vanessa-lapierre-cudnik/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Stephen Pacholski</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Director Digital Technology</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Pratt &amp; Whitney</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>stephen.pacholski@prattwhitney.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stephen-pacholski/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Roger Gattis</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Director of Infrastructure and Cloud Services</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>roger.gattis@us.abb.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roger-gattis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Marty Mason</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Senior System Administrator (Virtualization &amp; VDI)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>marty.mason@us.abb.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marty-mason/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Anthony Yuchnewicz</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>anthony.yuchnewicz@us.abb.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anthony-yuchnewicz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jeff Stoney</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Division Services Manager, Power Systems and Corporate</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>jeff.stoney@us.abb.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>derived-pattern</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jeff-stoney/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Eddie Poltl</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AVP IT Service Management / NOC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>eddie.poltl@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/search/?keywords=Eddie+Poltl+GM+Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Dale Conkel</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Global Infrastructure Solutions Architect II</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>dale.conkel@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/search/?keywords=Dale+Conkel+GM+Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Argha Das</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Global Network Engineer IV</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>argha.das@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/search/?keywords=Argha+Das+GM+Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Matt Guzman</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Global Network Engineer IV</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>matt.guzman@gmfinancial.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/search/?keywords=Matt+Guzman+GM+Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Deidre Meaney</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Director, IT Hardware Operations</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bonneville Power Administration</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>dmeaney@bpa.gov</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Gary Hood</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Supervisor, Network Services</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Bonneville Power Administration</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>gahood@bpa.gov</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Jeff Green</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Acting Director, Service Delivery</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Bonneville Power Administration</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>jlgreen@bpa.gov</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>John O'Donnell</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Manager, IT Platform Services</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Bonneville Power Administration</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>jpodonnell@bpa.gov</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Martie Marmolijo</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Mechanics Bank</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>martie_marmolijo@mechanicsbank.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Joeffrey Villegas</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Director, Network Engineering</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Mechanics Bank</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>joeffrey_villegas@mechanicsbank.com</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Michael Sevenandt</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Systems Engineer &amp; Manager</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Mechanics Bank</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>michael_sevenandt@mechanicsbank.com</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>6-email</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>existing-record</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Ryan Sawyer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Director, Infrastructure &amp; Service Delivery</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAANEeicBfsRA6aHCn8D5nh3Bb2DHhCXvtIA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (optics) / TPM / DIMMs</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sequence queued Day1=2026-06-04</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>8yr ISO NE career, Director Infra &amp; Service Delivery; April 2026 ISO-NE IT article hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Derek Rose</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Manager, Infrastructure Services</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAB2O3ZgBibIGN9srpBS3nZs9E6YHFAWrt2g</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server / TPM / Pre-Owned Networking</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Lou Catanzaro</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Network/Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Nuveen Investments</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAAACpsfYBYDVIx17PoBCxG-UGhZpxFBjHhQE,NAME_SEARCH,UFwm</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / TPM / DIMMs / Pre-Owned Networking</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Darron Nelson</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nuveen Investments</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/darron-nelson-3950b4a/</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server / TPM / Pre-Owned / Server Refresh</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Dom Waters</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Director of IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Live! Casino &amp; Hotel</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dom-adam-waters-1a726b6/</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / TPM / DIMMs / Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Ted Hartman</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Director - Data Center Operations</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IDEX Corporation</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ted-hartman-4bb68955/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / DIMMs / TPM / Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Paul Vetrano</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Senior Director - Enterprise Resilience</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulvetrano/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM / Transceivers / DIMMs / Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>David Maraffa</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Vice President Infrastructure</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Huntington Bancshares</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>david.maraffa@huntington.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>sample-offer-network</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>HubSpot 568759</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Confirmed current LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Clayton Harris</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Huntington Bancshares</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>clayton.harris@huntington.com</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>sample-offer-network</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>HubSpot 150344276094</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Confirmed current LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Vince Serritella</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Facility Data Center Manager</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Blue Cross Blue Shield Association</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>vince.serritella@bcbsa.com</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>sample-offer-network</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>HubSpot 191185245092</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Confirmed current LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Timothy Sime</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Senior Reliability Network Engineer</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>tsime@iso-ne.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / DWDM / DIMMs / TPM</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>HubSpot 567479</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Paul Burton</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Data Center Engineer</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>pburton@iso-ne.com</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / DWDM / DIMMs / TPM</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>HubSpot 567804</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Michal Dabrowski</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Lead Network Engineer</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>mdabrowski@iso-ne.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / DWDM / TPM</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>HubSpot 221681802501 (new)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Eric Whitmore</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Lead Network Engineer</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ewhitmore@iso-ne.com</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / DWDM / TPM</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>HubSpot 221680845673 (new)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Corey Slack</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Lead Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>cslack@iso-ne.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / DIMMs / TPM</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>HubSpot 221671177834 (new)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Nicholas Butkowski</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Supervisor, Shared Infrastructure Svcs</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>nbutkowski@iso-ne.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / TPM / DIMMs</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>HubSpot 221682034248 (new)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Franklin Henriquez</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Lead Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ISO New England</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>fhenriquez@iso-ne.com</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network / DIMMs / TPM</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>HubSpot 221672238098 (new)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Vince Illuzzi</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Managing Director Enterprise Technology Services - Systems Mgmt, Architecture &amp; Planning</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Nuveen Investments</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vince-illuzzi-ab3886/</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>HubSpot 355542 (existing). Dual scope unusual. Open to Work visible. Peter Bloom (360302) flagged DEPARTED - now at OURA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Ken Knicker</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IT Systems Architect/Engineer - Infrastructure Architecture &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Nuveen Investments</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LinkedIn: Ken K. - Infrastructure Architecture &amp; Engineering, Greater Chicago Area</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>HubSpot 221673056315 (new). MCITP/MCTS/MCSE. Minimal profile (shows as Ken K.). dominant-pattern email. ZoomInfo source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Daniel Khan</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Information Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Nuveen, a TIAA company</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LinkedIn: Information Systems Engineer at Nuveen, Summit NJ</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>HubSpot 221673637778 (new). Summit NJ office. dominant-pattern email. LinkedIn source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Spencer Poryles</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Infrastructure Technical Lead, Nuveen Natural Capital</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Nuveen Natural Capital</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LinkedIn: Infrastructure Technical Lead at Nuveen Natural Capital, Andover NJ</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>HubSpot 221673693055 (new). Andover NJ. Lean team for alternatives division. Systems + Infra + Cybersecurity. dominant-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jeff Morales</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>VP of IT Operations</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Live! Casino &amp; Hotel</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jeff-morales-4b344389/</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM (multi-property expansion); DIMMs secondary</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Aug 3</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Emerging Leaders 40U40 GGB; 12yr career; VA+LA openings 2025-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Jacent Molyneaux</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Live! Casino &amp; Hotel</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; DIMMs secondary</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Aug 7</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>ZI ID 11108540907</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Christo Leger</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sr Network and Telecom Engineer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Live! Casino &amp; Hotel</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sample-Offer Optics/Transceivers; TPM secondary</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Aug 13</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>ZI ID 2817328519; Laurel MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Jordan Renninger</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Live! Casino &amp; Hotel</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Sample-Offer Optics/Transceivers; TPM secondary</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Aug 19</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ZI ID 5953300628</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Rayburn Moore</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Senior System Engineer</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Live! Casino &amp; Hotel</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sample-Offer DIMMs; Compute secondary</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Aug 25</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ZI ID 1978579468; Baltimore MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Marcus Fletcher</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Live! Casino &amp; Hotel</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Sample-Offer DIMMs; Compute secondary</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Aug 31</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>ZI ID 8768200738</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Tania Osborne</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sr Director IT Operations</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>IDEX Corporation</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; DIMMs secondary</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Existing HubSpot</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Sep 4</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>LI: Infrastructure &amp; Ops Leader; M&amp;A integration; 2nd connection mutual Bruce Rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Thomas Magner</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Director IT Fire &amp; Safety NA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>IDEX Corporation</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; DIMMs secondary</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Existing HubSpot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Sep 10</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Divisional IT Director; Wooster OH</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Scott Yack</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IT Director IDEX Pneumatics Platform</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>IDEX Corporation</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; Compute/DIMMs secondary</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>New - ZI</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Sep 16</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>ZI ID -2049653092; Stevensville MI; 2nd connection mutual Bruce Rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Gary Bailey</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IDEX Corporation</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Sample-Offer DIMMs; Compute secondary</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>New - ZI</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Sep 22</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>ZI ID 8571798318; Star ID; 2nd connection mutual Bruce Rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Kimberly Caywood</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>VP Technology</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>UHG / Optum</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; multi-vendor Cisco/Dell/HP/NetApp</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Sep 28</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Stephen Babcock</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>UHG / Optum</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (400G transceiver); DWDM secondary</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Oct 2</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Michael Keyles</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>UHG / Optum</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Sample-Offer Compute/DIMMs; Dell/HP servers secondary</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Oct 8</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Tanner Herkert</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Network Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Cellcom</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (400G transceiver); DWDM secondary</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Existing HubSpot</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 19</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Shaun Grable</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IT Systems Manager</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cellcom</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Sample-Offer Compute/DIMMs; Dell/HP servers secondary</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 23</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t>Mufazzal Raghib</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="inlineStr">
+        <is>
+          <t>Director, Technology Solutions and Support Services</t>
+        </is>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>L.A. Care Health Plan</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="n"/>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM (Park Place renewal Q4); Compute/DIMMs; Pre-Owned Networking; Storage</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G123" s="17" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 18</t>
+        </is>
+      </c>
+      <c r="H123" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I123" s="17" t="n"/>
+      <c r="J123" s="17" t="n"/>
+      <c r="K123" s="17" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jeff Keller</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Gogo (formerly Satcom Direct)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM (Gogo/SD dual-legacy post-acquisition); DWDM (backbone capacity); Compute/DIMMs; Pre-Owned Networking</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 18</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>CIO promoted post-SD acquisition Dec 2024. 4 emails sent Aug 2025, 0 replies (8.5 mo ago). Email: jkeller@gogoair.com (dominant pattern 95.6%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jarrett Copija</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Vice President Information Technology</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gogo (formerly Satcom Direct)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM (inherited contracts post-acquisition); Compute/DIMMs; Pre-Owned Networking; DWDM</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 22</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Promoted from Sr Dir IT at Satcom Direct to VP IT at Gogo post-acquisition. Email: jcopija@gogoair.com (dominant pattern 95.6%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Richard Wilson</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Senior Network Architect</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gogo (formerly Satcom Direct)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (post-acquisition integration); TPM; DWDM; Pre-Owned Networking</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 29</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Moved to Gogo TechOps group post-SD acquisition. Email: rwilson@gogoair.com (dominant pattern 95.6%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>John Williams</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Director, Network &amp; Infrastructure Engineering Services</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>john_williams@intuit.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; Optics; Compute/DIMMs; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 18</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Rodrigo Allegretti</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Senior Manager, Network</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>rodrigo_allegretti@intuit.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network; TPM; DWDM; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Existing HubSpot - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 22</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jason Demello</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Global Sourcing and Procurement Leader</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>jason_demello@intuit.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; Compute/DIMMs; Storage; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 May 29</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Alan Hampton</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Data Center Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>alan_hampton@intuit.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; Compute/DIMMs; Optics; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Jun 4</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Dapo Adegeye</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Technology Strategic Sourcing Leader</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>dapo_adegeye@intuit.com</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; Compute/DIMMs; Storage; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Jun 10</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Stephen Epley</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Senior Manager, Mailchimp Infrastructure Engineering</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>stephen_epley@intuit.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network; TPM; Compute/DIMMs; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Jun 24</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Manikandan Kadarkarai</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Principal Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>manikandan_kadarkarai@intuit.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network; DWDM; TPM; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Existing HubSpot - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Jun 30</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Dexter Sale</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Manager, Reno Data Center Operations</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>dexter_sale@intuit.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM; Compute/DIMMs; Storage; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Jul 7</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Michael Proto</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sr. Storage Engineer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>michael_proto@intuit.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Pain-Led Storage/TPM; Compute/DIMMs; Optics; Pre-Owned</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>New - LinkedIn verified</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Sequence queued - E1 Jul 13</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Dennis Gallagher</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Dennis+Gallagher+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 221857066502)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-18</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>CTO. Sparse profile - employer verified via search snippet. 6 emails queued. Dominant pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Pete Gazsy</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Director of Network Services</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Pete+Gazsy+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Updated (ID: 311941) - title corrected</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Director of Network Services (promoted from Senior Supervisor). Existing HubSpot. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Kevin Kenny</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Director, Technology Services</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Kevin+Kenny+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Existing (ID: 183091117448)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-20</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Director Technology Services. Existing HubSpot contact. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Behzad Barzideh</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Senior Network Architect</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Behzad+Barzideh+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Existing (ID: 312183)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-21</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Senior Network Architect. Existing HubSpot contact. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sampurna Shrestha</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HPC &amp; Cloud Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Sampurna+Shrestha+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 221857360763)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-22</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>HPC and Cloud Enterprise Architect. Rare target. DDR4 DIMM angle for HPC. Dominant pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Matthew Oster</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Manager, Storage Engineering</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Matthew+Oster+Stony+Brook+Medicine+Storage</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Pain-Led Storage</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 221858250800)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-26</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Manager Storage Engineering. Separate from PCH Matthew Oster (ID 109376602544). Dominant pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Shrikant Iyer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Manager, Systems Engineering &amp; Support</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/siyer7/</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 221857583165)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-27</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Manager Systems Engineering. LinkedIn /in/siyer7/ confirmed. Dominant pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Orlando Capulong</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sr. Network Security Engineer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Orlando+Capulong+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Existing (ID: 412818)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-28</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Sr Network Security Engineer. Existing HubSpot contact. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Daniel Scotto</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>IT Director, Eastern Long Island Hospital</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Daniel+Scotto+Eastern+Long+Island+Hospital</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Existing (ID: 327920) - name fix pending manual update</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-05-29</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>IT Director ELIH (SBM affiliate). Email: dscotto@elih.org. HubSpot had 'Dan Scotto188' - auto update failed, manual fix needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Brigitte Borhi-Zahn</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Director, IT Integration</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Brigitte+Borhi-Zahn+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Existing (ID: 183091117455)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-06-01</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Director IT Integration. ZI FULL_MATCH brigitte.borhi-zahn@stonybrook.edu. Existing HubSpot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Edison Munizaga</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Edison+Munizaga+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 221857724581)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-06-02</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Network Engineer. Dominant pattern email. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Brian Mitchell</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Brian+Mitchell+Stony+Brook+Medicine+Systems</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 221868752716)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-06-03</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Systems Engineer. Dominant pattern email. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Jeff Bilello</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Stony Brook Medicine</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jeff+Bilello+Stony+Brook+Medicine</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Contact created (ID: 221857555358)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Sequence queued - Day 1 2026-06-04</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Cloud Engineer. Dominant pattern email. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Patrick Hwang</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>IT-CNP</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ACwAAB2kT-MBWYRjKqngLuwhF9el8zlhmdsxs8k</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SFPs)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Contact Created</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Sequence queued | LI task Jun 16</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>CCNA cert. Day 1: Jun 16. dominant-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Brian Garrett</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Data Center Support</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>IT-CNP</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Brian+Garrett+IT-CNP</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Sample-Offer Compute (DIMMs)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Contact Created</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Sequence queued | LI task Jun 23</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>13yr tenure. Day 1: Jun 23. dominant-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Dan Mosier</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Network Administrator</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>IT-CNP</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>No LinkedIn</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SFPs)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Contact Created</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Path B verified. No LinkedIn. Day 1: Jun 29. dominant-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Sal Baldwin</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>IT-CNP</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>No LinkedIn</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Sample-Offer Compute (DIMMs)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Contact Created</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Path B verified. No LinkedIn. Day 1: Jul 6. dominant-pattern email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Cynthia Gibson</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Unknown/Anonymous</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>IT-CNP</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LinkedIn not public</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>No action</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SKIP - Not ICP (anonymous LinkedIn, admin/ops role)</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>ZoomInfo email cgibson@it-cnp.com confirmed domain pattern only</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Lori Brown</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IT-CNP</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LinkedIn not public</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>No action</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SKIP - Not ICP (no role info)</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Only 2 LinkedIn-associated members; neither ICP</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Richard Burns</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Networking Specialist</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>IT-CNP</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>No LinkedIn</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>No action</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SKIP - ZoomInfo data stale (last updated 2020)</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Could not verify current employer. &gt;6 months stale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Brian Cundiff</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Sr Director, IT Infrastructure, Cloud &amp; Datacom</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>First Tech Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>In HubSpot</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-05-18</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Post-merger DCU+First Tech. Multi-vendor sprawl. TPM 40-60% below OEM. HubSpot ID 1435351.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Hayder Khzaali</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Principal Network Engineer</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>First Tech Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>In HubSpot</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-05-22</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Principal NE, optics for expanded footprint. HubSpot ID 185473606302. Prev rep touched Jan 2026, no sequence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Kashyap Desai</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>First Tech Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kashyap-desai-2013b8165/</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>New contact</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-05-29</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>CCNP-RS. Cisco focus. Post-merger network integration. HubSpot ID 221869486956.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Michael Porter</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sr Network Engineer</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>First Tech Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-porter-9b202b10/</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>New contact</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-06-04</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Sr NE, Roseville CA. California regional sites. HubSpot ID 221862444551.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>James Bull</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Sr Infrastructure IT Engineer, Storage &amp; Virtualization</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>First Tech Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jamesrbull/</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pain-Led Storage</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>New contact</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-06-10</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Storage+Virtualization. Post-merger storage consolidation. NetApp TPM angle. HubSpot ID 221868731180.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Clement Mugabo</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>First Tech Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>In HubSpot</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-06-24</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Sr NE, no outreach since 2020. HubSpot ID 1435751.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Soren Hampton</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sr System Engineer</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>First Tech Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/soren-hampton-9149b520a/</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>New contact</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-06-30</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Sr SE, Rancho Cordova CA. DIMM play, post-merger compute. HubSpot ID 221868568695.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Brett Aukburg</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>VP &amp; Head of Infrastructure</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>General Atlantic</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brettaukburg</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Call - TPM</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 191358868361)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-07-06</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>PE infra veteran: Bridgewater + Brandywine before GA. Lead TPM. HubSpot ID 191358868361.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>David Comeau</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sr Director Infrastructure Engineering, CISSP</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>General Atlantic</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/davidcomeau</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Call - Network (Optics)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 191358868362)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-07-10</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>14 yrs Caxton Associates data center + CISSP. Lead engineered transceivers. HubSpot ID 191358868362.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Steven Fonda</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sr Director Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>General Atlantic</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/steve-fonda-73031a8</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Call - Network (Optics)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 191358868350)</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-07-16</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>19 years at GA, built infrastructure from scratch. Lead optics sample offer. HubSpot ID 191358868350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Ahmed Sobhan</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Sr Network Engineer</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>General Atlantic</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ahmedsobhan</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Call - Network (Optics + DWDM)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 148959940104)</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-07-22</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Carrier background: Telstra + Link3 ISP. Deep optical expertise. Lead optics/DWDM. HubSpot ID 148959940104.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Nestor Cardona</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Compute &amp; Storage North America Manager</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nestor-cardona-b370a5a2/</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Call - Compute/Storage (DIMMs + Storage TPM)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>New contact (ID: 221872418566)</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-07-29</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>22 yrs at MUFG managing 15K servers + 900 VMware ESX hosts. Compute &amp; Storage NA Manager. DIMM/storage/server refresh play. HubSpot ID 221872418566.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Paul McLaughlin</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Network Engineer II</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paul-mclaughlin-68a6785/</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Call - Network (Sample-Offer)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>New contact (ID: 221872299270)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-08-04</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>26 years at Computershare. Manages AT&amp;T EVPN WAN + Cisco/Nokia/Nortel/Extreme gear. Very low LinkedIn presence, email primary. HubSpot ID 221872299270.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Gary Nowlan</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Network Delivery Engineer Global Technical Lead</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gary-nowlan/</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Call - Network (Sample-Offer)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>New contact (ID: 221874502964)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>E1 queued 2026-08-10</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Cisco Nexus/F5 LTM/GTM/Palo Alto background (Pegasystems 17 yrs). Global Tech Lead at Computershare since 2018. Hybrid DC + network. HubSpot ID 221874502964.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Michael McCaffrey</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Network Manager</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Computershare</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-mccaffrey-95b35953/</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Existing contact (ID: 315279) - SKIP</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Employer not verified</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>LinkedIn shows Computershare role ended Jul 2019. HubSpot record stale. Do not email. Verify before proceeding. HubSpot ID 315279.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19498,13 +26972,1590 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Tim Davidson</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>VP, IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tim-davidson-b1172851/</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>25 years VP IT Infrastructure at NFL. Day 1 = 2026-05-22. HubSpot ID 372153.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Gary Brantley</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>(SVP) Chief Information Officer</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/garybrantley/</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>SVP/CIO. Post about Accenture mtg 4d ago. Day 1=2026-05-29. HubSpot ID 219964123482.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Dave Port</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Vice President, Infrastructure</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dave-port-4330b255/</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>VP Infrastructure at NFL. ESPN acquisition angle. Day 1=2026-06-12. HubSpot ID 371713.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Aaron Amendolia</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Deputy CIO</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aaron-amendolia-6374ba6/</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Existing (reassigned)</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Deputy CIO at NFL. CrowdStrike outage hook. Existing HubSpot ID 371417 (was under John Houston). Day 1=2026-06-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Michael Brunton</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-brunton-8b76569/</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Network Engineer at NFL. Distributed Cisco footprint across stadiums/HQ. Dominant pattern email. HubSpot ID 220076717155. Day 1=2026-06-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Brian Krisburg</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Vice President, Procurement</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/briankrisburg/</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>VP Procurement at NFL. Park Place merger wedge. Mutual: Hans Oriol. HubSpot ID 220077415020. Day 1=2026-06-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Patrick Sellers</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-sellers-336bbb3</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>NE at NFL, Mt. Laurel NJ. 3rd+ connection. ZI nfl.net noted as alt. HubSpot ID 220070078215. Day 1=2026-07-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Richard Oh</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Sr. NE / CCNP</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richoh/</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Sr NE CCNP at NFL, Inglewood CA. SoFi hook. No ZI email. HubSpot ID 220046773430. Day 1=2026-07-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>John Noble</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Director Club &amp; Stadium IT</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-noble-07561912</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Director Club &amp; Stadium IT at NFL. ZI FULL_MATCH 99. Manages all 32 club IT environments. HubSpot ID 220070062396. Day 1=2026-07-16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Jason Hickok</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>VP, NFL Football Technology</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasonhickok/</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM + DIMMs</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>VP NFL Football Technology (Next Gen Stats, player tracking, instant replay). 22yr NFL veteran. ZI FULL_MATCH 98. HubSpot ID 532889 (updated from 2022 stub). Day 1=2026-07-22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Amanda Sarmiento</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Senior Manager, Technology Operations</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>LinkedIn InMail (2 tasks)</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Sr Manager Tech Ops at NFL. LinkedIn InMail only — no email sequence. HubSpot ID 220077498533. InMail 1=2026-05-21, InMail 2=2026-06-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>TreQuan Love</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Procurement Specialist</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tlove428/</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>IT Procurement, $75M+ annual NFL IT spend. Park Place/Service Express merger wedge. ZI FULL_MATCH 96. HubSpot ID 220086630318. Day 1=2026-07-29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Bennett Sciacca</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Procurement Operations</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>National Football League</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bennettsciacca/</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Sequence queued</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Sr. Manager Procurement Operations at NFL (Apr 2025). 10yrs NY Mets procurement. Email: bsciacca@nfl.com (ZI nonstandard). HubSpot ID 220073121653. Day 1=2026-08-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Pradip Patole</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Network Architect</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>linkedin.com/in/pradip-patole/</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | DWDM | DIMMs | TPM</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>6-email queued May 11</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>2xCCIE #49882 + OCSE optical cert</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Joe Tejeda</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Network Architect</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | DWDM | TPM | DIMMs</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>6-email queued May 15</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Network Architect at Miami International Airport</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Denis Ojalvo</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>6-email queued May 21</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>400+ Cisco Nexus devices</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Ming Ikehara</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Existing HubSpot contact (Aug 2024, cold since Sep 2024). LinkedIn gated. Company-level hook: NEC IT services + CSG acquisition. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Steven Godfrey</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Manager, Infrastructure</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | Compute/DIMMs</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Strongest buyer title at NEC (mgr-level, internal infra oversight). LinkedIn gated. Company-level hook: NEC IT services + CSG acquisition. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Nagharaj Kamatchireddiar</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-26</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Prior HubSpot record at OpenText (stale). New NEC record created. LinkedIn nearly empty. Company-level hook: NEC CSG acquisition. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Anthony Delanko</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>NEC Corporation of America</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-01</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>LinkedIn gated. Company-level hook: NEC IT services volume. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Kevin Parsons</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Senior Networking Engineer</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-13</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>LinkedIn confirmed via search (Colorado Springs CO). Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Vito Passalacqua</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-19</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>LinkedIn confirmed via search (Old Bridge NJ). Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Alex Burrell</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-05-26</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>In HubSpot since Sep 2025, never outreached. Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Chad Nelson</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Manager, IT Network</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Pain-Led</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-01</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Manager level - stronger buyer angle. Last contacted Sep 2024. Sales Nav browser rendered no cards. Company-level hook: Black Box networking push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Akhilesh Sharma</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-05</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Last contacted Sep 2024. Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Jason Westermeyer</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Black Box Network Services</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | TPM | Used Gear | DIMMs</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-22</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Last contacted Sep 2024. Sales Nav browser rendered no cards. Company-level hook: Black Box US networking demand push 2026. Cooling gap applied (6th person). 6 emails queued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Alfredo Gomez</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Ole Communications</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM | DIMMs/Compute | Pre-owned</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-04</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>No LinkedIn profile. ZoomInfo FULL_MATCH (personId 3866165102, accuracy 90). Email: acgomez@olecom.com. Ole FAST streaming expansion into Latin America / OTT anchor. Pain-Led TPM sequence. Email-only path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Kelvyn Abreu</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>IT Network - Media Production Support</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Ole Communications</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/lead/ACwAADwXap8B1dDYFMAPlfYWMNj0xxrpRxQojGM</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network | DIMMs/Compute | TPM | Pre-owned</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>New - Sequenced</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>6-email queued - Day 1 2026-06-10</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>LinkedIn profile confirmed (Sales Nav). ZoomInfo personId 8156440628, accuracy 85. Email kabreu@olecom.com derived from verified olecom.com pattern. Led WatchGuard-to-Ubiquiti migration + Proxmox VMs. IC-level but hardware decision-maker at 76-person media company. Job-seeking signal noted. Ole stagger person 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Octavio Arauz</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Broadcast Operations Center Technician</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Ole Communications</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>No ICP fit</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Disqualified</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>NO - Broadcast ops; maintains on-air signal quality, not a hardware buyer</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Career: Sprint retail &gt; Entercom board op &gt; iHeartMedia broadcast &gt; Ole BOC. Top skill: Social Media (2). Zero networking/infra. BOC role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Lizette Arocha</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Production and Network Operations Coordinator for Golf Channel Latin America</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Ole Communications</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>No ICP fit</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Disqualified</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>NO - Broadcast distribution coordinator; Network = broadcast, not IP networking</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>6 months tenure. Broadcast signal distribution, not IT infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Ricardo Antillano</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Ole Communications</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>No ICP fit</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Disqualified</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>NO - Broadcast TV operations executive; all broadcast skills, zero networking/infra</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Electronics Engineering + MBA. 14 yrs HBO LAG + VP E! Entertainment LatinAmerica. Top skills: Television (39), Broadcast TV (36), Video Production (31).</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Eduardo Cusco</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Ole Communications</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>No ICP fit</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Disqualified</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>NO - Completely empty profile; cannot determine VP of what</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>No About, no skills, no descriptions. 1 employer, 102 connections. Unqualifiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>DongHoon Shin</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Server Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>JMARK</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMMs)</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Sequence queued, Day 1 2026-06-16</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>6 emails queued. Dominant-pattern email dshin@jmark.com. Follow-up: TPM, Dell/HP servers, storage. HubSpot ID 221866974244.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Jim Neal</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Network Engineer III</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>JMARK</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SFPs)</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Sequence queued, Day 1 2026-06-23</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>6 emails queued. Dominant-pattern email jneal@jmark.com. Follow-up: TPM, pre-owned Cisco, DWDM. HubSpot ID 221854566556.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Tony Beabout</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>VP Managed Services</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>JMARK</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>PENDING-NEEDS-HOOK. LI connect set 2026-06-10.</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Qualified YES but Email 1 not queued. Tenure-only hook (thin). Fresh hook: JMARK Tulsa office Nov 2025. Revisit LinkedIn for recent post/project. Sequence Day 1 ~2026-06-29 once hook found. HubSpot ID 221868257687.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Louis DePasquale</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>JMARK</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>No ICP fit</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Not targeted</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Thin profile, skipped. No qualifying signals.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20997,7 +30048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21132,7 +30183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22356,4 +31407,74 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Date Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>T-Mobile</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Not a target for Auto Mode (too large / strategic only)</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Panasonic</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Not a target for Auto Mode (complex org / strategic only)</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:K248"/>
+  <dimension ref="A2:K264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -11630,6 +11630,703 @@
       <c r="H248" t="inlineStr">
         <is>
           <t>2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Randy Kulman</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>VP, Network Operations &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/randy-kulman-89375350/</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (transceivers), DWDM, TPM, Pre-Owned Networking</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>6-email sequence queued Day 1 2026-05-28</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Dominant-pattern email rkulman@dobson.net. 12+ fiber builds OK/AR May 2026. 6,500-mile network. ZI credits exhausted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>William Zayas</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Vice President, Network Engineering</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/williamzayas/</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Pain-Led DWDM, Optics Sample, TPM, Pre-Owned Networking</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>6-email sequence queued Day 1 2026-06-03</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Dominant-pattern wzayas@dobson.net. DWDM explicit in headline. 12 new routes OK/AR May 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Raymond Castor</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>rcastor@dobson.net</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Pain-Led TPM</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Thomas Claydon</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Sr. Network Systems Engineer</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>tclaydon@dobson.net</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Jason Estridge</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>jestridge@dobson.net</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Travis Hedger</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Network Engineer III</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>thedger@dobson.net</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Evon Williams</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Optical Network Engineer</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ewilliams@dobson.net</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>dominant-pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>William Zayas</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>VP Network Engineering</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>wzayas@dobson.net</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Pain-Led DWDM</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>hubspot-existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Carl Brown</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>cbrown@dobson.net</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>dominant-pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Danny Abbott</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Dobson Technologies</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>dabbott@dobson.net</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>dominant-pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Joshua Bradley</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>jbradley@dobson.net</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>dominant-pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Jacquie Cossey</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Network Provisioning</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>jcossey@dobson.net</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>dominant-pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Adam Cavazos</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>VP Network Systems &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Dobson Fiber</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>acavazos@dobson.net</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Pain-Led DWDM</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>dominant-pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Andy Hulscher</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Chief Operations Officer</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Alliance Communications</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andy-hulscher-04886b6/</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Email sequence queued Day 1 2026-05-29</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>dominant-pattern email andyh@alliance.coop | CFO retired May 8 2026 after 30 yrs + Luverne MN fiber expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Derek Ridgway</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Network Administrator</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Alliance Communications</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/derek-ridgway-676ba2148/</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Email sequence queued Day 1 2026-06-04</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>verified-pattern email derekr@alliance.coop (ZI FULL_MATCH score 94) | CFO retired May 8 2026 + Luverne MN expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Darin Egenes</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Systems Administrator</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Alliance Communications</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/darin-egenes-7180842/</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Sequence Active</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Email sequence queued Day 1 2026-06-10</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>dominant-pattern email darine@alliance.coop | Path A verified LinkedIn | remote Seattle WA | CFO retired May 8 2026 + Luverne MN expansion</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:K264"/>
+  <dimension ref="A2:K271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -12327,6 +12327,335 @@
       <c r="I264" t="inlineStr">
         <is>
           <t>dominant-pattern email darine@alliance.coop | Path A verified LinkedIn | remote Seattle WA | CFO retired May 8 2026 + Luverne MN expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Friedrich Seifts</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Vice President: Technology Operations</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Index Exchange</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fseifts/</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMM), TPM + optics follow</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Contact created 226189354417</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Sequence drafted to AI fields, enroll Day 1 2026-06-04</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Hook: MLB/Disney Streaming infra builder; Index Cloud buildout Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Michael O'Dea</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Director of System Operations</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Index Exchange</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/modea/</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMM), TPM + storage follow</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Contact created 226188750943</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Sequence drafted to AI fields, enroll Day 1 2026-06-10</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Hook: joined Apr 2026 from Disney Streaming (7 yrs infra); ex MLBAM/BAMTech</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Tony Savor</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>VP, Platform Engineering</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Index Exchange</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tony-savor-7869271/</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMM), optics + TPM + storage follow</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Contact created 226189889046</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Sequence drafted to AI fields, enroll Day 1 2026-06-16</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Hook: ex Google GKE + Facebook storage infra; planet scale efficiency posts; U of T on prem research</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Bo Blanton</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Director, Data Systems</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Index Exchange</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wyndham/</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMM), storage + TPM follow</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Contact created 226186213420</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Sequence drafted to AI fields, enroll Day 1 2026-06-22</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Hook: Berkeley chem PhD to petabyte data systems; ex ASAPP with Seifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Luis Alfredo Morales Lora</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Engineering Lead Manager - Network Engineering</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Index Exchange</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-alfredo-morales-lora-182ba684/</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SFP), DWDM + pre-owned + TPM follow</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Contact created 226186662295</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Sequence drafted to AI fields, enroll Day 1 2026-06-26</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Hook: CCIE 47341 RS|SP; AlticeDo ISP backbone to Cisco to IX network engineering lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Joshua Hoblitt</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Staff Storage Engineer</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Index Exchange</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jhoblitt/</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Sample-Offer Server (DIMM), storage + TPM follow</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Contact created 226207041068</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Sequence drafted to AI fields, enroll Day 1 2026-07-13</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Hook: joined ~Feb 2026; shared Rook v1.19.5 Ceph release last month</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Edward Alvarez</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Staff Network Engineer</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Index Exchange</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edward-alvarez-9893573b/</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Sample-Offer Network (SFP), pre-owned + DWDM + TPM follow</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Contact created 226206123378</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Sequence drafted to AI fields, enroll Day 1 2026-07-17</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Hook: AlticeDo to SIG to IX network; RIT MS; same lineage as manager Luis</t>
         </is>
       </c>
     </row>

--- a/prospects-tracker-new.xlsx
+++ b/prospects-tracker-new.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mini\Documents\osi-claude-brain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\osi-claude-brain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1F7FB2-A4C6-4334-A53C-05474D7CCCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17ED24D-B2D6-4E86-A685-F07F8EE733E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7665" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37215" yWindow="7935" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
   <si>
     <t>Name</t>
   </si>
@@ -179,6 +179,48 @@
   </si>
   <si>
     <t>No email found. LinkedIn InMail path. Server Engineer at SBG -- DIMMs wedge for 6-ISP compute standardization.</t>
+  </si>
+  <si>
+    <t>Joe Brannan</t>
+  </si>
+  <si>
+    <t>VP Core Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Lincoln Financial Group</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/joe-brannan-6828634/</t>
+  </si>
+  <si>
+    <t>Pain-Led TPM (DIMMs, pre-owned Cisco, optics secondary)</t>
+  </si>
+  <si>
+    <t>Sequenced</t>
+  </si>
+  <si>
+    <t>Enroll in HubSpot sequence 2026-06-12</t>
+  </si>
+  <si>
+    <t>joe.brannan@lfg.com | direct +1 (336) 860-5805 | mobile +1 (336) 681-4949 | HubSpot ID 227841622697</t>
+  </si>
+  <si>
+    <t>Dan Vetro</t>
+  </si>
+  <si>
+    <t>VP Infrastructure, UCC, Network and Contact Center</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/danvetro/</t>
+  </si>
+  <si>
+    <t>Pain-Led TPM (optics, pre-owned Cisco, DIMMs secondary)</t>
+  </si>
+  <si>
+    <t>Enroll in HubSpot sequence 2026-06-18</t>
+  </si>
+  <si>
+    <t>dan.vetro@lfg.com | no phone (ZI no record) | HubSpot ID 227837492758 | email: dominant-pattern</t>
   </si>
 </sst>
 </file>
@@ -533,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -680,6 +722,64 @@
       </c>
       <c r="I5" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="2">
+        <v>46184</v>
+      </c>
+      <c r="I6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="2">
+        <v>46184</v>
+      </c>
+      <c r="I7" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
